--- a/docs/review/packs/chapter-3.2.xlsx
+++ b/docs/review/packs/chapter-3.2.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Expect a test to load more than one degree of freedom, and read a combination of findings rather than one.</t>
+          <t>State the flexion angle whenever a laxity figure is recorded, because the same knee gives different answers at different angles.</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Treat the six as a set whose members trade against each other.</t>
+          <t>Compare with the other side rather than with a published range, since individual variation exceeds most injury effects in the smaller degrees of freedom.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation as well as translation before accepting that a knee is stable, since the instrument exists for one and not the other.</t>
+          <t>Expect a test to load more than one degree of freedom, and read a combination of findings rather than one.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Consider what a construct constrains beyond its target, because the trade is real and is reported by patients as stiffness rather than as over-constraint.</t>
+          <t>Treat the six as a set whose members trade against each other.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Avoid describing a knee as stable on the basis of the degree of freedom that happens to have an instrument.</t>
+          <t>Assess rotation as well as translation before accepting that a knee is stable, since the instrument exists for one and not the other.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -2066,22 +2066,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P1</t>
+          <t>3.2.1-P6</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Expect effusion to limit flexion early, and reassess range once it has settled rather than recording a limited range as fixed.</t>
+          <t>Consider what a construct constrains beyond its target, because the trade is real and is reported by patients as stiffness rather than as over-constraint.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -2091,12 +2091,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P2</t>
+          <t>3.2.1-P7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Treat the flexion arc as the product of surface geometry and ligament length, and note that surgery can alter either independently.</t>
+          <t>Avoid describing a knee as stable on the basis of the degree of freedom that happens to have an instrument.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2116,7 +2116,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P3</t>
+          <t>3.2.2-P1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Measure extension deliberately rather than as part of a sweep, since small deficits are both the hardest to measure and the most disabling.</t>
+          <t>Expect effusion to limit flexion early, and reassess range once it has settled rather than recording a limited range as fixed.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P4</t>
+          <t>3.2.2-P2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Consider slope and offset when a knee does not achieve its expected arc after surgery.</t>
+          <t>Treat the flexion arc as the product of surface geometry and ligament length, and note that surgery can alter either independently.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P5</t>
+          <t>3.2.2-P3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting a design's published flexion as a patient's expected flexion.</t>
+          <t>Measure extension deliberately rather than as part of a sweep, since small deficits are both the hardest to measure and the most disabling.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,22 +2191,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P1</t>
+          <t>3.2.2-P4</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Expect a combined anterior cruciate and anterolateral injury to produce more rotation than either alone.</t>
+          <t>Consider slope and offset when a knee does not achieve its expected arc after surgery.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,12 +2216,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P2</t>
+          <t>3.2.2-P5</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Treat internal rotation as the degree of freedom that exposes the limits of current practice: it is the motion patients complain about, the one surgery most often fails to restore, and the one with no number.</t>
+          <t>Avoid quoting a design's published flexion as a patient's expected flexion.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P3</t>
+          <t>3.2.3-P1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Consider an anterolateral procedure where rotational laxity is high, and understand it as restoring a distributed restraint rather than replacing a structure.</t>
+          <t>Grade the pivot shift and record the grade, because it is the only routine measure of this motion.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P4</t>
+          <t>3.2.3-P2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Avoid reading a normal arthrometer reading as a stable knee.</t>
+          <t>Expect a combined anterior cruciate and anterolateral injury to produce more rotation than either alone.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,22 +2291,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P1</t>
+          <t>3.2.3-P3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterior cruciate in any knee with increased external rotation at 90 degrees.</t>
+          <t>Treat internal rotation as the degree of freedom that exposes the limits of current practice: it is the motion patients complain about, the one surgery most often fails to restore, and the one with no number.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,12 +2316,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P2</t>
+          <t>3.2.3-P4</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Treat increased external rotation as a localising sign rather than a severity measure.</t>
+          <t>Grade and document rotation at every assessment, since the absence of an instrument makes the serial record the only comparison available.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,12 +2341,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P3</t>
+          <t>3.2.3-P5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment in any knee with a posterolateral finding, before planning a soft tissue procedure.</t>
+          <t>Consider an anterolateral procedure where rotational laxity is high, and understand it as restoring a distributed restraint rather than replacing a structure.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P4</t>
+          <t>3.2.3-P6</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
+          <t>Set expectations in terms of rotation rather than translation, because that is what patients describe.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,22 +2391,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P1</t>
+          <t>3.2.3-P7</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment on a long leg film in any knee with coronal laxity, because the two together decide the treatment.</t>
+          <t>Avoid reading a normal arthrometer reading as a stable knee.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,12 +2416,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P2</t>
+          <t>3.2.4-P1</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Expect laxity and alignment to drive each other, which is the argument for correcting alignment alongside any lateral reconstruction.</t>
+          <t>Examine the posterior cruciate in any knee with increased external rotation at 90 degrees.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,22 +2441,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P3</t>
+          <t>3.2.4-P2</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Treat varus as a system rather than a sign.</t>
+          <t>Compare sides rather than using an absolute threshold, since baseline rotation varies between people.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P4</t>
+          <t>3.2.4-P3</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Measure on weight bearing films, since a supine measurement describes an unloaded knee.</t>
+          <t>Treat increased external rotation as a localising sign rather than a severity measure.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P5</t>
+          <t>3.2.4-P4</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Avoid reconstructing laxity in a limb whose alignment caused it.</t>
+          <t>Assess alignment in any knee with a posterolateral finding, before planning a soft tissue procedure.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,22 +2516,22 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P1</t>
+          <t>3.2.4-P5</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Examine the anterior cruciate in any complete medial injury.</t>
+          <t>Read continuity on imaging as insufficient to exclude a corner injury, since tissue heals long.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,22 +2541,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P2</t>
+          <t>3.2.4-P6</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Treat bracing as a mechanical intervention aimed at healing position, and explain it that way.</t>
+          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,22 +2566,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P3</t>
+          <t>3.2.5-P1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Treat medial laxity as a question about length rather than continuity.</t>
+          <t>Measure alignment on a long leg film in any knee with coronal laxity, because the two together decide the treatment.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P4</t>
+          <t>3.2.5-P2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment before reconstructing chronic medial laxity, since a valgus limb protects a medial reconstruction and a varus one does not.</t>
+          <t>Expect laxity and alignment to drive each other, which is the argument for correcting alignment alongside any lateral reconstruction.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,12 +2616,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P5</t>
+          <t>3.2.5-P3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Consider shortening rather than only reattaching in a chronic injury, because the problem is length.</t>
+          <t>Treat varus as a system rather than a sign.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P6</t>
+          <t>3.2.5-P4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Avoid reading continuity on imaging as competence.</t>
+          <t>Correct alignment before or with a lateral reconstruction in a varus limb, and say so in the plan rather than treating it as optional.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,22 +2666,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P1</t>
+          <t>3.2.5-P5</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Examine the menisci in a chronic cruciate deficient knee, because the secondary restraint is under load and fails over time.</t>
+          <t>Measure on weight bearing films, since a supine measurement describes an unloaded knee.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,22 +2691,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P2</t>
+          <t>3.2.5-P6</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Measure side to side rather than absolute, since baseline laxity varies widely.</t>
+          <t>Avoid reconstructing laxity in a limb whose alignment caused it.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,12 +2716,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P3</t>
+          <t>3.2.6-P1</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Avoid concluding that a knee is stable from a normal arthrometer reading alone.</t>
+          <t>Examine the anterior cruciate in any complete medial injury.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,22 +2741,22 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P4</t>
+          <t>3.2.6-P2</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat anterior translation as a partial description of anterior instability.</t>
+          <t>Treat bracing as a mechanical intervention aimed at healing position, and explain it that way.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P5</t>
+          <t>3.2.6-P3</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation alongside translation before judging a reconstruction, since only one of the two has an instrument.</t>
+          <t>Treat medial laxity as a question about length rather than continuity.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,12 +2791,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P6</t>
+          <t>3.2.6-P4</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a revision, because it is a modifiable bony cause of a repeated ligamentous failure.</t>
+          <t>Delay the decision in an isolated medial injury where the anatomy says healing is likely, and re-examine rather than operating on the first finding.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,12 +2816,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P7</t>
+          <t>3.2.6-P5</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue in a cruciate deficient knee, since the secondary restraint protects the primary one and the graft that replaces it.</t>
+          <t>Assess alignment before reconstructing chronic medial laxity, since a valgus limb protects a medial reconstruction and a varus one does not.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,12 +2841,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P8</t>
+          <t>3.2.6-P6</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating a measured translation as the outcome of interest when the patient's complaint is rotational.</t>
+          <t>Consider shortening rather than only reattaching in a chronic injury, because the problem is length.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P1</t>
+          <t>3.2.6-P7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterolateral corner in every posterior cruciate injury, since the combination changes the treatment.</t>
+          <t>Avoid reading continuity on imaging as competence.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,12 +2891,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P2</t>
+          <t>3.2.7-P1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Expect downhill and stair symptoms rather than rotational giving way.</t>
+          <t>Examine the menisci in a chronic cruciate deficient knee, because the secondary restraint is under load and fails over time.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,22 +2916,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P3</t>
+          <t>3.2.7-P2</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Treat the posterior cruciate as the restraint and the corner as the modifier.</t>
+          <t>Measure side to side rather than absolute, since baseline laxity varies widely.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,22 +2941,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P4</t>
+          <t>3.2.7-P3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Measure with stress radiography where the grade decides the treatment, rather than relying on a clinical estimate from an uncertain starting position.</t>
+          <t>Avoid concluding that a knee is stable from a normal arthrometer reading alone.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P5</t>
+          <t>3.2.7-P4</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment in any chronic posterolateral injury before planning reconstruction.</t>
+          <t>Treat anterior translation as a partial description of anterior instability.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,12 +2991,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P6</t>
+          <t>3.2.7-P5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Expect partial healing and reassess rather than treating the early finding as final.</t>
+          <t>Assess rotation alongside translation before judging a reconstruction, since only one of the two has an instrument.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,12 +3016,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P7</t>
+          <t>3.2.7-P6</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Avoid reconstructing a posterior cruciate in a varus limb without addressing the alignment.</t>
+          <t>Measure slope in a revision, because it is a modifiable bony cause of a repeated ligamentous failure.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P1</t>
+          <t>3.2.7-P7</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Expect a knee with a meniscal and a ligament injury to behave worse than either alone, because both act on the same path.</t>
+          <t>Preserve meniscal tissue in a cruciate deficient knee, since the secondary restraint protects the primary one and the graft that replaces it.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P2</t>
+          <t>3.2.7-P8</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Treat coupling as the reason rotatory laxity and translational laxity dissociate after reconstruction.</t>
+          <t>Avoid treating a measured translation as the outcome of interest when the patient's complaint is rotational.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P3</t>
+          <t>3.2.8-P1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation as well as translation before calling a reconstruction successful.</t>
+          <t>Read the resting step off before pushing.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,22 +3116,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P4</t>
+          <t>3.2.8-P2</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Consider the coupled contribution of slope and lateral plateau shape when a graft fails without a new injury.</t>
+          <t>Examine the posterolateral corner in every posterior cruciate injury, since the combination changes the treatment.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P5</t>
+          <t>3.2.8-P3</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Repair or preserve the lateral meniscus posterior horn where possible, on mechanical grounds related to the coupled motion.</t>
+          <t>Read an intact posterior cruciate on imaging as compatible with laxity, because healing in continuity at length is common.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,22 +3166,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P1</t>
+          <t>3.2.8-P4</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Expect a patient with a ligament injury to improve with rehabilitation without the ligament healing, since the muscular share can be increased.</t>
+          <t>Expect downhill and stair symptoms rather than rotational giving way.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,22 +3191,22 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P2</t>
+          <t>3.2.8-P5</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Treat giving way as a report of the path being lost rather than as a report of pain, and ask what the knee was doing at the time.</t>
+          <t>Treat the posterior cruciate as the restraint and the corner as the modifier.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,22 +3216,22 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P3</t>
+          <t>3.2.8-P6</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Expect examination under anaesthetic to show more laxity than the clinic, and plan around the larger figure.</t>
+          <t>Measure with stress radiography where the grade decides the treatment, rather than relying on a clinical estimate from an uncertain starting position.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,22 +3241,22 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P4</t>
+          <t>3.2.8-P7</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Treat the muscular contribution as modifiable and the ligamentous one as not, which is the basis of non operative management in selected injuries.</t>
+          <t>Assess alignment in any chronic posterolateral injury before planning reconstruction.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P5</t>
+          <t>3.2.8-P8</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Treat stability as a system with redundancy rather than as a set of independent structures.</t>
+          <t>Expect partial healing and reassess rather than treating the early finding as final.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,12 +3291,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P6</t>
+          <t>3.2.8-P9</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Plan multiligament reconstruction around the system rather than structure by structure, since restoring one restraint changes the load on the others.</t>
+          <t>Avoid reconstructing a posterior cruciate in a varus limb without addressing the alignment.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,31 +3316,356 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P7</t>
+          <t>3.2.9-P1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue in an unstable knee, because it carries both restraint and load distribution.</t>
+          <t>Read a rotatory test as the more informative one when anterior cruciate function is in question, since it loads the coupled pair.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-P2</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Expect a knee with a meniscal and a ligament injury to behave worse than either alone, because both act on the same path.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-P3</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Treat coupling as the reason rotatory laxity and translational laxity dissociate after reconstruction.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-P4</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Assess rotation as well as translation before calling a reconstruction successful.</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-P5</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Consider the coupled contribution of slope and lateral plateau shape when a graft fails without a new injury.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-P6</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Repair or preserve the lateral meniscus posterior horn where possible, on mechanical grounds related to the coupled motion.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P1</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Expect a patient with a ligament injury to improve with rehabilitation without the ligament healing, since the muscular share can be increased.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P2</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Treat giving way as a report of the path being lost rather than as a report of pain, and ask what the knee was doing at the time.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P3</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Expect examination under anaesthetic to show more laxity than the clinic, and plan around the larger figure.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P4</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Treat the muscular contribution as modifiable and the ligamentous one as not, which is the basis of non operative management in selected injuries.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P5</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Treat stability as a system with redundancy rather than as a set of independent structures.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P6</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Plan multiligament reconstruction around the system rather than structure by structure, since restoring one restraint changes the load on the others.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P7</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment where it is loading a reconstruction, on mechanical grounds rather than on appearance.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P8</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Preserve meniscal tissue in an unstable knee, because it carries both restraint and load distribution.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5053,7 +5378,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>56</f>
+        <f>69</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -5068,7 +5393,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -5098,7 +5423,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -5110,7 +5435,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5122,7 +5447,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -5134,7 +5459,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E58,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E71,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.2.xlsx
+++ b/docs/review/packs/chapter-3.2.xlsx
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -1852,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Avoid describing a knee as stable on the basis of the degree of freedom that happens to have an instrument.</t>
+          <t>Record laxity with its flexion angle and its comparison side, so a later assessment can be read against it.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -2116,22 +2116,22 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P1</t>
+          <t>3.2.1-P8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Expect effusion to limit flexion early, and reassess range once it has settled rather than recording a limited range as fixed.</t>
+          <t>Avoid describing a knee as stable on the basis of the degree of freedom that happens to have an instrument.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -2141,7 +2141,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P2</t>
+          <t>3.2.2-P1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Treat the flexion arc as the product of surface geometry and ligament length, and note that surgery can alter either independently.</t>
+          <t>Record two numbers and name the deficit, because an arc alone conceals fixed flexion.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P3</t>
+          <t>3.2.2-P2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Measure extension deliberately rather than as part of a sweep, since small deficits are both the hardest to measure and the most disabling.</t>
+          <t>Expect effusion to limit flexion early, and reassess range once it has settled rather than recording a limited range as fixed.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2191,7 +2191,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P4</t>
+          <t>3.2.2-P3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Consider slope and offset when a knee does not achieve its expected arc after surgery.</t>
+          <t>Treat the flexion arc as the product of surface geometry and ligament length, and note that surgery can alter either independently.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-P5</t>
+          <t>3.2.2-P4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Avoid quoting a design's published flexion as a patient's expected flexion.</t>
+          <t>Measure extension deliberately rather than as part of a sweep, since small deficits are both the hardest to measure and the most disabling.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2241,22 +2241,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P1</t>
+          <t>3.2.2-P5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Grade the pivot shift and record the grade, because it is the only routine measure of this motion.</t>
+          <t>Record passive and active range separately when assessing a stiff knee, because the difference localises the cause.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2266,22 +2266,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P2</t>
+          <t>3.2.2-P6</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Expect a combined anterior cruciate and anterolateral injury to produce more rotation than either alone.</t>
+          <t>Consider slope and offset when a knee does not achieve its expected arc after surgery.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2291,12 +2291,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P3</t>
+          <t>3.2.2-P7</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Treat internal rotation as the degree of freedom that exposes the limits of current practice: it is the motion patients complain about, the one surgery most often fails to restore, and the one with no number.</t>
+          <t>Avoid quoting a design's published flexion as a patient's expected flexion.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P4</t>
+          <t>3.2.3-P1</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Grade and document rotation at every assessment, since the absence of an instrument makes the serial record the only comparison available.</t>
+          <t>Grade the pivot shift and record the grade, because it is the only routine measure of this motion.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P5</t>
+          <t>3.2.3-P2</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Consider an anterolateral procedure where rotational laxity is high, and understand it as restoring a distributed restraint rather than replacing a structure.</t>
+          <t>Expect a combined anterior cruciate and anterolateral injury to produce more rotation than either alone.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P6</t>
+          <t>3.2.3-P3</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Set expectations in terms of rotation rather than translation, because that is what patients describe.</t>
+          <t>Treat internal rotation as the degree of freedom that exposes the limits of current practice: it is the motion patients complain about, the one surgery most often fails to restore, and the one with no number.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -2391,7 +2391,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-P7</t>
+          <t>3.2.3-P4</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Avoid reading a normal arthrometer reading as a stable knee.</t>
+          <t>Grade and document rotation at every assessment, since the absence of an instrument makes the serial record the only comparison available.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -2416,22 +2416,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P1</t>
+          <t>3.2.3-P5</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterior cruciate in any knee with increased external rotation at 90 degrees.</t>
+          <t>Consider an anterolateral procedure where rotational laxity is high, and understand it as restoring a distributed restraint rather than replacing a structure.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -2441,22 +2441,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P2</t>
+          <t>3.2.3-P6</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Compare sides rather than using an absolute threshold, since baseline rotation varies between people.</t>
+          <t>Set expectations in terms of rotation rather than translation, because that is what patients describe.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -2466,12 +2466,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P3</t>
+          <t>3.2.3-P7</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Treat increased external rotation as a localising sign rather than a severity measure.</t>
+          <t>Avoid reading a normal arthrometer reading as a stable knee.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P4</t>
+          <t>3.2.4-P1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment in any knee with a posterolateral finding, before planning a soft tissue procedure.</t>
+          <t>Examine the posterior cruciate in any knee with increased external rotation at 90 degrees.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P5</t>
+          <t>3.2.4-P2</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Read continuity on imaging as insufficient to exclude a corner injury, since tissue heals long.</t>
+          <t>Compare sides rather than using an absolute threshold, since baseline rotation varies between people.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -2541,7 +2541,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-P6</t>
+          <t>3.2.4-P3</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
+          <t>Treat increased external rotation as a localising sign rather than a severity measure.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -2566,22 +2566,22 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P1</t>
+          <t>3.2.4-P4</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Measure alignment on a long leg film in any knee with coronal laxity, because the two together decide the treatment.</t>
+          <t>Assess alignment in any knee with a posterolateral finding, before planning a soft tissue procedure.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -2591,22 +2591,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P2</t>
+          <t>3.2.4-P5</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Expect laxity and alignment to drive each other, which is the argument for correcting alignment alongside any lateral reconstruction.</t>
+          <t>Read continuity on imaging as insufficient to exclude a corner injury, since tissue heals long.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -2616,12 +2616,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P3</t>
+          <t>3.2.4-P6</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Treat varus as a system rather than a sign.</t>
+          <t>Record both dial angles and the side difference at every assessment, since this is the one rotation with a serial number available.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -2641,12 +2641,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P4</t>
+          <t>3.2.4-P7</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment before or with a lateral reconstruction in a varus limb, and say so in the plan rather than treating it as optional.</t>
+          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -2666,7 +2666,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P5</t>
+          <t>3.2.5-P1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Measure on weight bearing films, since a supine measurement describes an unloaded knee.</t>
+          <t>Measure alignment on a long leg film in any knee with coronal laxity, because the two together decide the treatment.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-P6</t>
+          <t>3.2.5-P2</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Avoid reconstructing laxity in a limb whose alignment caused it.</t>
+          <t>Expect laxity and alignment to drive each other, which is the argument for correcting alignment alongside any lateral reconstruction.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -2716,22 +2716,22 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P1</t>
+          <t>3.2.5-P3</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Examine the anterior cruciate in any complete medial injury.</t>
+          <t>Treat varus as a system rather than a sign.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2741,22 +2741,22 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P2</t>
+          <t>3.2.5-P4</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Treat bracing as a mechanical intervention aimed at healing position, and explain it that way.</t>
+          <t>Correct alignment before or with a lateral reconstruction in a varus limb, and say so in the plan rather than treating it as optional.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P3</t>
+          <t>3.2.5-P5</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Treat medial laxity as a question about length rather than continuity.</t>
+          <t>Measure on weight bearing films, since a supine measurement describes an unloaded knee.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -2791,12 +2791,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P4</t>
+          <t>3.2.5-P6</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Delay the decision in an isolated medial injury where the anatomy says healing is likely, and re-examine rather than operating on the first finding.</t>
+          <t>Record thrust explicitly, because it predicts the mechanical environment a construct will live in.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2816,12 +2816,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P5</t>
+          <t>3.2.5-P7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment before reconstructing chronic medial laxity, since a valgus limb protects a medial reconstruction and a varus one does not.</t>
+          <t>Avoid reconstructing laxity in a limb whose alignment caused it.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P6</t>
+          <t>3.2.6-P1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Consider shortening rather than only reattaching in a chronic injury, because the problem is length.</t>
+          <t>Examine the anterior cruciate in any complete medial injury.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-P7</t>
+          <t>3.2.6-P2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Avoid reading continuity on imaging as competence.</t>
+          <t>Treat bracing as a mechanical intervention aimed at healing position, and explain it that way.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2891,22 +2891,22 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P1</t>
+          <t>3.2.6-P3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Examine the menisci in a chronic cruciate deficient knee, because the secondary restraint is under load and fails over time.</t>
+          <t>Treat medial laxity as a question about length rather than continuity.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2916,22 +2916,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P2</t>
+          <t>3.2.6-P4</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Measure side to side rather than absolute, since baseline laxity varies widely.</t>
+          <t>Delay the decision in an isolated medial injury where the anatomy says healing is likely, and re-examine rather than operating on the first finding.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2941,22 +2941,22 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P3</t>
+          <t>3.2.6-P5</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Avoid concluding that a knee is stable from a normal arthrometer reading alone.</t>
+          <t>Assess alignment before reconstructing chronic medial laxity, since a valgus limb protects a medial reconstruction and a varus one does not.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P4</t>
+          <t>3.2.6-P6</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Treat anterior translation as a partial description of anterior instability.</t>
+          <t>Consider shortening rather than only reattaching in a chronic injury, because the problem is length.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2991,12 +2991,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P5</t>
+          <t>3.2.6-P7</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation alongside translation before judging a reconstruction, since only one of the two has an instrument.</t>
+          <t>Avoid reading continuity on imaging as competence.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -3016,7 +3016,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P6</t>
+          <t>3.2.7-P1</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Measure slope in a revision, because it is a modifiable bony cause of a repeated ligamentous failure.</t>
+          <t>Examine the menisci in a chronic cruciate deficient knee, because the secondary restraint is under load and fails over time.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -3041,7 +3041,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P7</t>
+          <t>3.2.7-P2</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue in a cruciate deficient knee, since the secondary restraint protects the primary one and the graft that replaces it.</t>
+          <t>Measure side to side rather than absolute, since baseline laxity varies widely.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -3066,7 +3066,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-P8</t>
+          <t>3.2.7-P3</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating a measured translation as the outcome of interest when the patient's complaint is rotational.</t>
+          <t>Avoid concluding that a knee is stable from a normal arthrometer reading alone.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -3091,22 +3091,22 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P1</t>
+          <t>3.2.7-P4</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Read the resting step off before pushing.</t>
+          <t>Treat anterior translation as a partial description of anterior instability.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -3116,22 +3116,22 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P2</t>
+          <t>3.2.7-P5</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Examine the posterolateral corner in every posterior cruciate injury, since the combination changes the treatment.</t>
+          <t>Assess rotation alongside translation before judging a reconstruction, since only one of the two has an instrument.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -3141,22 +3141,22 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P3</t>
+          <t>3.2.7-P6</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Read an intact posterior cruciate on imaging as compatible with laxity, because healing in continuity at length is common.</t>
+          <t>Measure slope in a revision, because it is a modifiable bony cause of a repeated ligamentous failure.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -3166,22 +3166,22 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P4</t>
+          <t>3.2.7-P7</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Expect downhill and stair symptoms rather than rotational giving way.</t>
+          <t>Preserve meniscal tissue in a cruciate deficient knee, since the secondary restraint protects the primary one and the graft that replaces it.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -3191,12 +3191,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P5</t>
+          <t>3.2.7-P8</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Treat the posterior cruciate as the restraint and the corner as the modifier.</t>
+          <t>Avoid treating a measured translation as the outcome of interest when the patient's complaint is rotational.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -3216,7 +3216,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P6</t>
+          <t>3.2.8-P1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Measure with stress radiography where the grade decides the treatment, rather than relying on a clinical estimate from an uncertain starting position.</t>
+          <t>Read the resting step off before pushing.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -3241,7 +3241,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P7</t>
+          <t>3.2.8-P2</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Assess alignment in any chronic posterolateral injury before planning reconstruction.</t>
+          <t>Examine the posterolateral corner in every posterior cruciate injury, since the combination changes the treatment.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -3266,7 +3266,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P8</t>
+          <t>3.2.8-P3</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Expect partial healing and reassess rather than treating the early finding as final.</t>
+          <t>Read an intact posterior cruciate on imaging as compatible with laxity, because healing in continuity at length is common.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-P9</t>
+          <t>3.2.8-P4</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Avoid reconstructing a posterior cruciate in a varus limb without addressing the alignment.</t>
+          <t>Expect downhill and stair symptoms rather than rotational giving way.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -3316,22 +3316,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P1</t>
+          <t>3.2.8-P5</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Read a rotatory test as the more informative one when anterior cruciate function is in question, since it loads the coupled pair.</t>
+          <t>Treat the posterior cruciate as the restraint and the corner as the modifier.</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -3341,22 +3341,22 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P2</t>
+          <t>3.2.8-P6</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Expect a knee with a meniscal and a ligament injury to behave worse than either alone, because both act on the same path.</t>
+          <t>Measure with stress radiography where the grade decides the treatment, rather than relying on a clinical estimate from an uncertain starting position.</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -3366,12 +3366,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P3</t>
+          <t>3.2.8-P7</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Treat coupling as the reason rotatory laxity and translational laxity dissociate after reconstruction.</t>
+          <t>Assess alignment in any chronic posterolateral injury before planning reconstruction.</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -3391,12 +3391,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P4</t>
+          <t>3.2.8-P8</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Assess rotation as well as translation before calling a reconstruction successful.</t>
+          <t>Expect partial healing and reassess rather than treating the early finding as final.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -3416,12 +3416,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P5</t>
+          <t>3.2.8-P9</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>3.2.9</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Consider the coupled contribution of slope and lateral plateau shape when a graft fails without a new injury.</t>
+          <t>Avoid reconstructing a posterior cruciate in a varus limb without addressing the alignment.</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>3.2.9-P6</t>
+          <t>3.2.9-P1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Repair or preserve the lateral meniscus posterior horn where possible, on mechanical grounds related to the coupled motion.</t>
+          <t>Read a rotatory test as the more informative one when anterior cruciate function is in question, since it loads the coupled pair.</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -3466,22 +3466,22 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P1</t>
+          <t>3.2.9-P2</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Expect a patient with a ligament injury to improve with rehabilitation without the ligament healing, since the muscular share can be increased.</t>
+          <t>Record the coupled findings together in posterolateral injury rather than grading varus alone.</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -3491,22 +3491,22 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P2</t>
+          <t>3.2.9-P3</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Treat giving way as a report of the path being lost rather than as a report of pain, and ask what the knee was doing at the time.</t>
+          <t>Expect a knee with a meniscal and a ligament injury to behave worse than either alone, because both act on the same path.</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -3516,22 +3516,22 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P3</t>
+          <t>3.2.9-P4</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Expect examination under anaesthetic to show more laxity than the clinic, and plan around the larger figure.</t>
+          <t>Treat coupling as the reason rotatory laxity and translational laxity dissociate after reconstruction.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -3541,22 +3541,22 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P4</t>
+          <t>3.2.9-P5</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Treat the muscular contribution as modifiable and the ligamentous one as not, which is the basis of non operative management in selected injuries.</t>
+          <t>Assess rotation as well as translation before calling a reconstruction successful.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -3566,12 +3566,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P5</t>
+          <t>3.2.9-P6</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Treat stability as a system with redundancy rather than as a set of independent structures.</t>
+          <t>Consider the coupled contribution of slope and lateral plateau shape when a graft fails without a new injury.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3591,12 +3591,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P6</t>
+          <t>3.2.9-P7</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.9</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Plan multiligament reconstruction around the system rather than structure by structure, since restoring one restraint changes the load on the others.</t>
+          <t>Repair or preserve the lateral meniscus posterior horn where possible, on mechanical grounds related to the coupled motion.</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P7</t>
+          <t>3.2.10-P1</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Correct alignment where it is loading a reconstruction, on mechanical grounds rather than on appearance.</t>
+          <t>Expect a patient with a ligament injury to improve with rehabilitation without the ligament healing, since the muscular share can be increased.</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3641,7 +3641,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-P8</t>
+          <t>3.2.10-P2</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -3651,21 +3651,171 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Preserve meniscal tissue in an unstable knee, because it carries both restraint and load distribution.</t>
+          <t>Treat giving way as a report of the path being lost rather than as a report of pain, and ask what the knee was doing at the time.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P3</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Expect examination under anaesthetic to show more laxity than the clinic, and plan around the larger figure.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P4</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Treat the muscular contribution as modifiable and the ligamentous one as not, which is the basis of non operative management in selected injuries.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P5</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Treat stability as a system with redundancy rather than as a set of independent structures.</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P6</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Plan multiligament reconstruction around the system rather than structure by structure, since restoring one restraint changes the load on the others.</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P7</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Correct alignment where it is loading a reconstruction, on mechanical grounds rather than on appearance.</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-P8</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Preserve meniscal tissue in an unstable knee, because it carries both restraint and load distribution.</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E3:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
+    <dataValidation sqref="E3:E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: CONFIRMED, AMENDED, WITHDRAWN, NOT_CLINICAL" type="list">
       <formula1>"CONFIRMED,AMENDED,WITHDRAWN,NOT_CLINICAL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5378,7 +5528,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>69</f>
+        <f>75</f>
         <v/>
       </c>
       <c r="C2" s="3">
@@ -5393,7 +5543,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"&lt;&gt;")</f>
+        <f>COUNTIF(Recommendations!E3:E77,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="3">
@@ -5423,7 +5573,7 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"CONFIRMED")</f>
+        <f>COUNTIF(Recommendations!E3:E77,"CONFIRMED")</f>
         <v/>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -5435,7 +5585,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"AMENDED")</f>
+        <f>COUNTIF(Recommendations!E3:E77,"AMENDED")</f>
         <v/>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5447,7 +5597,7 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"WITHDRAWN")</f>
+        <f>COUNTIF(Recommendations!E3:E77,"WITHDRAWN")</f>
         <v/>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -5459,7 +5609,7 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Recommendations!E3:E71,"NOT_CLINICAL")</f>
+        <f>COUNTIF(Recommendations!E3:E77,"NOT_CLINICAL")</f>
         <v/>
       </c>
       <c r="C8" s="3" t="inlineStr"/>

--- a/docs/review/packs/chapter-3.2.xlsx
+++ b/docs/review/packs/chapter-3.2.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -3829,7 +3829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>140 degrees</t>
+          <t>six degrees</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives flexion and extension about 140 degrees, axial rotation up to about 30 degrees at 90 degrees of flexion, varus and valgus a few degrees, anteroposterior translation about 5 to 10 mm, and medial to lateral translation and compression to distraction one or two millimetres each.</t>
+          <t>A rigid body in space has six degrees of freedom: it can rotate about three axes and translate along three.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>140 degrees</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>90 degrees</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>5 to 10 mm</t>
+          <t>90 degrees</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>25 to 30 degrees</t>
+          <t>5 to 10 mm</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Axial rotation is close to zero in full extension and conventional teaching puts it at about 25 to 30 degrees total at 90 degrees of flexion.</t>
+          <t>Conventional teaching gives flexion and extension about 140 degrees, axial rotation up to about 30 degrees at 90 degrees of flexion, varus and valgus a few degrees, anteroposterior translation about 5 to 10 mm, and medial to lateral translation and compression to distraction one or two millimetres each.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
@@ -4075,12 +4075,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F1</t>
+          <t>3.2.1-F6</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>0 to 140 degrees</t>
+          <t>one or two millimetres</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives the range as about 0 to 140 degrees, with 5 to 10 degrees of hyperextension present in many normal knees.</t>
+          <t>Conventional teaching gives flexion and extension about 140 degrees, axial rotation up to about 30 degrees at 90 degrees of flexion, varus and valgus a few degrees, anteroposterior translation about 5 to 10 mm, and medial to lateral translation and compression to distraction one or two millimetres each.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -4105,12 +4105,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F2</t>
+          <t>3.2.1-F7</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>5 to 10 degrees</t>
+          <t>one degree</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives the range as about 0 to 140 degrees, with 5 to 10 degrees of hyperextension present in many normal knees.</t>
+          <t>Every stability test is an attempt to isolate one degree of freedom and measure it.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -4135,27 +4135,27 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F3</t>
+          <t>3.2.1-F8</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3.2.2</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>0 to 60 degrees</t>
+          <t>25 to 30 degrees</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
+          <t>Axial rotation is close to zero in full extension and conventional teaching puts it at about 25 to 30 degrees total at 90 degrees of flexion.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -4165,7 +4165,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F4</t>
+          <t>3.2.2-F1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -4173,19 +4173,15 @@
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>medical_student</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>ten degrees</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
+          <t>The knee's largest motion, the ranges that daily life needs, and why the last ten degrees of extension matter more than the last thirty of flexion.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -4195,7 +4191,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F5</t>
+          <t>3.2.2-F2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -4210,12 +4206,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0 to 140 degrees</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
+          <t>Conventional teaching gives the range as about 0 to 140 degrees, with 5 to 10 degrees of hyperextension present in many normal knees.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -4225,7 +4221,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F6</t>
+          <t>3.2.2-F3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4240,12 +4236,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>5 to 10 degrees</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
+          <t>Conventional teaching gives the range as about 0 to 140 degrees, with 5 to 10 degrees of hyperextension present in many normal knees.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -4255,7 +4251,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F7</t>
+          <t>3.2.2-F4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -4270,13 +4266,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>30
-degrees</t>
+          <t>0 to 60 degrees</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Effusion limits flexion before anything else does, because the capsule has a volume at which it is most comfortable and that volume corresponds to about 30 degrees.</t>
+          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -4286,7 +4281,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F8</t>
+          <t>3.2.2-F5</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4301,12 +4296,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>10 degrees</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Losing the last 10 degrees of extension is more disabling than losing the last 30 of flexion.</t>
+          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -4316,7 +4311,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F9</t>
+          <t>3.2.2-F6</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -4331,12 +4326,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Losing the last 10 degrees of extension is more disabling than losing the last 30 of flexion.</t>
+          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -4346,7 +4341,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F10</t>
+          <t>3.2.2-F7</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -4356,17 +4351,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>20 degrees</t>
+          <t>130</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Rolling without gliding would roll the femur off the back of the tibia within about 20 degrees.</t>
+          <t>Level walking uses about 0 to 60 degrees, stairs about 80 to 90, sitting about 90, and squatting beyond 130.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -4376,7 +4371,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F11</t>
+          <t>3.2.2-F8</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -4386,17 +4381,18 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>15 mm</t>
+          <t>30
+degrees</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching puts the tibiofemoral contact point moving posteriorly by of the order of 15 mm from extension to deep flexion in the lateral compartment and considerably less medially.</t>
+          <t>Effusion limits flexion before anything else does, because the capsule has a volume at which it is most comfortable and that volume corresponds to about 30 degrees.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -4406,7 +4402,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F12</t>
+          <t>3.2.2-F9</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -4416,17 +4412,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>10 to 120 degrees</t>
+          <t>10 degrees</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Recording convention matters: a knee described as having 10 to 120 degrees has a fixed flexion deformity, and the same arc described as 110 degrees of movement hides it.</t>
+          <t>Losing the last 10 degrees of extension is more disabling than losing the last 30 of flexion.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -4436,7 +4432,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3.2.2-F13</t>
+          <t>3.2.2-F10</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -4446,17 +4442,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>110 degrees</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Recording convention matters: a knee described as having 10 to 120 degrees has a fixed flexion deformity, and the same arc described as 110 degrees of movement hides it.</t>
+          <t>Losing the last 10 degrees of extension is more disabling than losing the last 30 of flexion.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -4466,27 +4462,27 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-F1</t>
+          <t>3.2.2-F11</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10 to 15 degrees</t>
+          <t>20 degrees</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives internal rotation of about 10 to 15 degrees at 90 degrees of flexion.</t>
+          <t>Rolling without gliding would roll the femur off the back of the tibia within about 20 degrees.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -4496,27 +4492,27 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-F2</t>
+          <t>3.2.2-F12</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>90 degrees</t>
+          <t>15 mm</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives internal rotation of about 10 to 15 degrees at 90 degrees of flexion.</t>
+          <t>Conventional teaching puts the tibiofemoral contact point moving posteriorly by of the order of 15 mm from extension to deep flexion in the lateral compartment and considerably less medially.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -4526,12 +4522,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-F3</t>
+          <t>3.2.2-F13</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -4541,12 +4537,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>25 to 30 degrees</t>
+          <t>10 to 120 degrees</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Total axial rotation, internal and external together, is conventionally given as about 25 to 30 degrees at 90 degrees of flexion, with external rotation taking the larger share.</t>
+          <t>Recording convention matters: a knee described as having 10 to 120 degrees has a fixed flexion deformity, and the same arc described as 110 degrees of movement hides it.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -4556,12 +4552,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>3.2.3-F4</t>
+          <t>3.2.2-F14</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>3.2.3</t>
+          <t>3.2.2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4571,12 +4567,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110 degrees</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>The pivot shift is graded 0 to 3 by feel, and interobserver agreement is moderate at best.</t>
+          <t>Recording convention matters: a knee described as having 10 to 120 degrees has a fixed flexion deformity, and the same arc described as 110 degrees of movement hides it.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -4586,27 +4582,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F1</t>
+          <t>3.2.3-F1</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>medical_student</t>
-        </is>
-      </c>
+          <t>3.2.3</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>15 to 20 degrees</t>
+          <t>ninety degrees</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives external rotation of about 15 to 20 degrees at 90 degrees of flexion, somewhat more than internal rotation at the same angle.</t>
+          <t>Turning the shin inwards under the thigh: almost impossible straight, freest at ninety degrees, and the motion a pivot shift is made of.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -4616,12 +4608,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F2</t>
+          <t>3.2.3-F2</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4631,13 +4623,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>90
-degrees</t>
+          <t>10 to 15 degrees</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives external rotation of about 15 to 20 degrees at 90 degrees of flexion, somewhat more than internal rotation at the same angle.</t>
+          <t>Conventional teaching gives internal rotation of about 10 to 15 degrees at 90 degrees of flexion.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -4647,12 +4638,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F3</t>
+          <t>3.2.3-F3</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4662,12 +4653,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>90 degrees</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Posterolateral injury increases it, and the increase is larger at 30 degrees than at 90 when the posterior cruciate is intact.</t>
+          <t>Conventional teaching gives internal rotation of about 10 to 15 degrees at 90 degrees of flexion.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -4677,27 +4668,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F4</t>
+          <t>3.2.3-F4</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>25 to 30 degrees</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Posterolateral injury increases it, and the increase is larger at 30 degrees than at 90 when the posterior cruciate is intact.</t>
+          <t>Total axial rotation, internal and external together, is conventionally given as about 25 to 30 degrees at 90 degrees of flexion, with external rotation taking the larger share.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -4707,27 +4698,27 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F5</t>
+          <t>3.2.3-F5</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3.2.4</t>
+          <t>3.2.3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>The dial test measures external rotation at 30 and at 90 degrees and compares sides.</t>
+          <t>The pivot shift is graded 0 to 3 by feel, and interobserver agreement is moderate at best.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -4737,7 +4728,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F6</t>
+          <t>3.2.4-F1</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -4752,12 +4743,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>30 and 90 degrees</t>
+          <t>15 to 20 degrees</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>- The dial test measures it at 30 and 90 degrees and compares sides.</t>
+          <t>Conventional teaching gives external rotation of about 15 to 20 degrees at 90 degrees of flexion, somewhat more than internal rotation at the same angle.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -4767,7 +4758,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F7</t>
+          <t>3.2.4-F2</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -4777,17 +4768,18 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>10 degrees</t>
+          <t>90
+degrees</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>A side to side difference of more than about 10 degrees is the conventional threshold for a positive test.</t>
+          <t>Conventional teaching gives external rotation of about 15 to 20 degrees at 90 degrees of flexion, somewhat more than internal rotation at the same angle.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -4797,7 +4789,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>3.2.4-F8</t>
+          <t>3.2.4-F3</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -4807,17 +4799,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>frcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>10 degree</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
+          <t>Posterolateral injury increases it, and the increase is larger at 30 degrees than at 90 when the posterior cruciate is intact.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -4827,12 +4819,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-F1</t>
+          <t>3.2.4-F4</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -4842,12 +4834,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>At about 30 degrees of flexion the capsule and cruciates contribute less, so the test is done at that angle to isolate the collateral ligament.</t>
+          <t>Posterolateral injury increases it, and the increase is larger at 30 degrees than at 90 when the posterior cruciate is intact.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -4857,27 +4849,27 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3.2.5-F2</t>
+          <t>3.2.4-F5</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>3.2.5</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0 and 30 degrees</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Test at 0 and 30 degrees and read the pair, since the pattern separates the collateral from the corner.</t>
+          <t>The dial test measures external rotation at 30 and at 90 degrees and compares sides.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -4887,12 +4879,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-F1</t>
+          <t>3.2.4-F6</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -4902,12 +4894,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>5 to 7 degrees</t>
+          <t>30 and 90 degrees</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives physiological valgus alignment as about 5 to 7 degrees, with women on average slightly higher than men.</t>
+          <t>- The dial test measures it at 30 and 90 degrees and compares sides.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -4917,27 +4909,27 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-F2</t>
+          <t>3.2.4-F7</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>20 to 30 degrees</t>
+          <t>10 degrees</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Testing at 20 to 30 degrees of flexion isolates the collateral ligament, because the secondary restraints contribute less there.</t>
+          <t>A side to side difference of more than about 10 degrees is the conventional threshold for a positive test.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -4947,27 +4939,27 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-F3</t>
+          <t>3.2.4-F8</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>25 degrees</t>
+          <t>two centimetres</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>The superficial collateral carries the large majority of valgus restraint at 25 degrees of flexion, with the posteromedial corner taking an increasing share towards extension.</t>
+          <t>The corner's restraint is shared between three structures within two centimetres of each other, which is why the test localises to a region and not to a ligament.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -4977,27 +4969,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-F4</t>
+          <t>3.2.4-F9</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>frcs</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>10 degree</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching grades medial injury by the opening at 30 degrees: a few millimetres for grade one and two, and a complete loss of endpoint for grade three.</t>
+          <t>Avoid treating the 10 degree threshold as a boundary rather than a convention.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -5007,27 +4999,27 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>3.2.6-F5</t>
+          <t>3.2.5-F1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>3.2.6</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0 and 30 degrees</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Valgus stress testing at 0 and 30 degrees, graded by opening and endpoint.</t>
+          <t>At about 30 degrees of flexion the capsule and cruciates contribute less, so the test is done at that angle to isolate the collateral ligament.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -5037,27 +5029,27 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F1</t>
+          <t>3.2.5-F2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>85 per cent</t>
+          <t>0 and 30 degrees</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives its share as about 85 per cent of the resistance to anterior translation.</t>
+          <t>Test at 0 and 30 degrees and read the pair, since the pattern separates the collateral from the corner.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -5067,12 +5059,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F2</t>
+          <t>3.2.6-F1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -5082,12 +5074,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>5 to 10 mm</t>
+          <t>5 to 7 degrees</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives normal anterior translation as about 5 to 10 mm at 30 degrees of flexion, with the side to side difference being the clinically useful quantity.</t>
+          <t>Conventional teaching gives physiological valgus alignment as about 5 to 7 degrees, with women on average slightly higher than men.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -5097,12 +5089,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F3</t>
+          <t>3.2.6-F2</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -5112,12 +5104,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>20 to 30 degrees</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives normal anterior translation as about 5 to 10 mm at 30 degrees of flexion, with the side to side difference being the clinically useful quantity.</t>
+          <t>Testing at 20 to 30 degrees of flexion isolates the collateral ligament, because the secondary restraints contribute less there.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -5127,27 +5119,27 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F4</t>
+          <t>3.2.6-F3</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>medical_student</t>
+          <t>mrcs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>25 degrees</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Translation is largest around 30 degrees, which is why the Lachman test is done there rather than at 90.</t>
+          <t>The superficial collateral carries the large majority of valgus restraint at 25 degrees of flexion, with the posteromedial corner taking an increasing share towards extension.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -5157,12 +5149,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F5</t>
+          <t>3.2.6-F4</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -5172,12 +5164,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>3 mm</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives a side to side difference of more than about 3 mm on instrumented testing as the usual threshold for abnormality.</t>
+          <t>Conventional teaching grades medial injury by the opening at 30 degrees: a few millimetres for grade one and two, and a complete loss of endpoint for grade three.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -5187,12 +5179,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F6</t>
+          <t>3.2.6-F5</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3.2.7</t>
+          <t>3.2.6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -5202,12 +5194,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>7 to 10 degrees</t>
+          <t>0 and 30 degrees</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Posterior tibial slope increases anterior translation under axial load, with conventional teaching putting normal slope at about 7 to 10 degrees.</t>
+          <t>Valgus stress testing at 0 and 30 degrees, graded by opening and endpoint.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -5217,7 +5209,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3.2.7-F7</t>
+          <t>3.2.7-F1</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -5225,19 +5217,15 @@
           <t>3.2.7</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>mrcs</t>
-        </is>
-      </c>
+      <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>one degree</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Instrumented arthrometry applies a known force and measures displacement, usually at about 134 newtons, and reports side to side difference.</t>
+          <t>The one degree of freedom with a clinical instrument, and the one most often mistaken for the whole problem.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -5247,12 +5235,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F1</t>
+          <t>3.2.7-F2</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -5262,12 +5250,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>95 per cent</t>
+          <t>85 per cent</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives its share as about 95 per cent of the resistance to posterior translation at 90 degrees of flexion.</t>
+          <t>Conventional teaching gives its share as about 85 per cent of the resistance to anterior translation.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
@@ -5277,12 +5265,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F2</t>
+          <t>3.2.7-F3</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -5292,12 +5280,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>90 degrees</t>
+          <t>5 to 10 mm</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching gives its share as about 95 per cent of the resistance to posterior translation at 90 degrees of flexion.</t>
+          <t>Conventional teaching gives normal anterior translation as about 5 to 10 mm at 30 degrees of flexion, with the side to side difference being the clinically useful quantity.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -5307,12 +5295,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F3</t>
+          <t>3.2.7-F4</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -5322,12 +5310,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>10 mm</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching puts the normal step off at about 10 mm of tibia in front of the condyle at 90 degrees of flexion.</t>
+          <t>Conventional teaching gives normal anterior translation as about 5 to 10 mm at 30 degrees of flexion, with the side to side difference being the clinically useful quantity.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -5337,27 +5325,27 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F4</t>
+          <t>3.2.7-F5</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0 to 5 mm</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching grades by step off: 0 to 5 mm grade one, 5 to 10 mm grade two, more than 10 mm grade three.</t>
+          <t>Translation is largest around 30 degrees, which is why the Lachman test is done there rather than at 90.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -5367,12 +5355,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F5</t>
+          <t>3.2.7-F6</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -5382,12 +5370,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>5 to 10 mm</t>
+          <t>3 mm</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Conventional teaching grades by step off: 0 to 5 mm grade one, 5 to 10 mm grade two, more than 10 mm grade three.</t>
+          <t>Conventional teaching gives a side to side difference of more than about 3 mm on instrumented testing as the usual threshold for abnormality.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
@@ -5397,12 +5385,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>3.2.8-F6</t>
+          <t>3.2.7-F7</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>3.2.8</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -5412,12 +5400,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7 to 10 degrees</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>- Conventional teaching grades by step off: 0 to 5, 5 to 10, and more than 10 mm.</t>
+          <t>Posterior tibial slope increases anterior translation under axial load, with conventional teaching putting normal slope at about 7 to 10 degrees.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -5427,12 +5415,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-F1</t>
+          <t>3.2.7-F8</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.7</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -5442,12 +5430,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>The handover from bone to soft tissue occurs over roughly the first 30 degrees of flexion, which is why the same test gives different answers at 0 and 30 degrees.</t>
+          <t>Instrumented arthrometry applies a known force and measures displacement, usually at about 134 newtons, and reports side to side difference.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -5457,36 +5445,306 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>3.2.10-F2</t>
+          <t>3.2.8-F1</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>3.2.10</t>
+          <t>3.2.8</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>mrcs</t>
+          <t>medical_student</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0 and 30 degrees</t>
+          <t>95 per cent</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>The handover from bone to soft tissue occurs over roughly the first 30 degrees of flexion, which is why the same test gives different answers at 0 and 30 degrees.</t>
+          <t>Conventional teaching gives its share as about 95 per cent of the resistance to posterior translation at 90 degrees of flexion.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8-F2</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>90 degrees</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Conventional teaching gives its share as about 95 per cent of the resistance to posterior translation at 90 degrees of flexion.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8-F3</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>10 mm</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Conventional teaching puts the normal step off at about 10 mm of tibia in front of the condyle at 90 degrees of flexion.</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8-F4</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>0 to 5 mm</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Conventional teaching grades by step off: 0 to 5 mm grade one, 5 to 10 mm grade two, more than 10 mm grade three.</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8-F5</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>5 to 10 mm</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Conventional teaching grades by step off: 0 to 5 mm grade one, 5 to 10 mm grade two, more than 10 mm grade three.</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8-F6</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>- Conventional teaching grades by step off: 0 to 5, 5 to 10, and more than 10 mm.</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-F1</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>one degree</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Coupled motion means that moving a joint in one degree of freedom produces motion in another, without any separate effort to create it.</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9-F2</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>medical_student</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>six degrees</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>The six degrees of freedom described in 3.2.1 are therefore a vocabulary rather than a list of independent movements.</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-F1</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>30 degrees</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>The handover from bone to soft tissue occurs over roughly the first 30 degrees of flexion, which is why the same test gives different answers at 0 and 30 degrees.</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10-F2</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>mrcs</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>0 and 30 degrees</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>The handover from bone to soft tissue occurs over roughly the first 30 degrees of flexion, which is why the same test gives different answers at 0 and 30 degrees.</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F3:F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: VERIFIED, CORRECTED, REMOVED" type="list">
+    <dataValidation sqref="F3:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: VERIFIED, CORRECTED, REMOVED" type="list">
       <formula1>"VERIFIED,CORRECTED,REMOVED"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5532,7 +5790,7 @@
         <v/>
       </c>
       <c r="C2" s="3">
-        <f>52</f>
+        <f>61</f>
         <v/>
       </c>
     </row>
@@ -5547,7 +5805,7 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIF(Measurements!F3:F54,"&lt;&gt;")</f>
+        <f>COUNTIF(Measurements!F3:F63,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -5622,7 +5880,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3">
-        <f>COUNTIF(Measurements!F3:F54,"VERIFIED")</f>
+        <f>COUNTIF(Measurements!F3:F63,"VERIFIED")</f>
         <v/>
       </c>
     </row>
@@ -5634,7 +5892,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3">
-        <f>COUNTIF(Measurements!F3:F54,"CORRECTED")</f>
+        <f>COUNTIF(Measurements!F3:F63,"CORRECTED")</f>
         <v/>
       </c>
     </row>
@@ -5646,7 +5904,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3">
-        <f>COUNTIF(Measurements!F3:F54,"REMOVED")</f>
+        <f>COUNTIF(Measurements!F3:F63,"REMOVED")</f>
         <v/>
       </c>
     </row>
